--- a/CodeSystem-dk-npu-fragment.xlsx
+++ b/CodeSystem-dk-npu-fragment.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-10T08:40:47+00:00</t>
+    <t>2024-05-10T19:12:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-npu-fragment.xlsx
+++ b/CodeSystem-dk-npu-fragment.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-10T19:12:38+00:00</t>
+    <t>2024-05-12T08:40:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-npu-fragment.xlsx
+++ b/CodeSystem-dk-npu-fragment.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-12T08:40:34+00:00</t>
+    <t>2024-05-12T08:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-npu-fragment.xlsx
+++ b/CodeSystem-dk-npu-fragment.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:12:53+00:00</t>
+    <t>2024-06-25T21:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-npu-fragment.xlsx
+++ b/CodeSystem-dk-npu-fragment.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:21:07+00:00</t>
+    <t>2024-06-25T21:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-npu-fragment.xlsx
+++ b/CodeSystem-dk-npu-fragment.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:20:43+00:00</t>
+    <t>2024-06-25T21:42:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-npu-fragment.xlsx
+++ b/CodeSystem-dk-npu-fragment.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-25T21:42:34+00:00</t>
+    <t>2024-06-26T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-npu-fragment.xlsx
+++ b/CodeSystem-dk-npu-fragment.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-26T14:36:19+00:00</t>
+    <t>2024-06-27T10:47:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-npu-fragment.xlsx
+++ b/CodeSystem-dk-npu-fragment.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-27T10:47:07+00:00</t>
+    <t>2024-08-11T15:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-npu-fragment.xlsx
+++ b/CodeSystem-dk-npu-fragment.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-11T15:57:41+00:00</t>
+    <t>2024-10-17T12:12:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-npu-fragment.xlsx
+++ b/CodeSystem-dk-npu-fragment.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="109">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T06:07:37+00:00</t>
+    <t>2024-10-27T12:31:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -179,6 +179,84 @@
   </si>
   <si>
     <t>boolean</t>
+  </si>
+  <si>
+    <t>ChangeDate</t>
+  </si>
+  <si>
+    <t>https://iupac.org/fhir/npu/concept-properties#ChangeDate</t>
+  </si>
+  <si>
+    <t>CreatedDate</t>
+  </si>
+  <si>
+    <t>https://iupac.org/fhir/npu/concept-properties#CreatedDate</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>https://iupac.org/fhir/npu/concept-properties#System</t>
+  </si>
+  <si>
+    <t>SysSpec</t>
+  </si>
+  <si>
+    <t>https://iupac.org/fhir/npu/concept-properties#SysSpec</t>
+  </si>
+  <si>
+    <t>Component</t>
+  </si>
+  <si>
+    <t>https://iupac.org/fhir/npu/concept-properties#Component</t>
+  </si>
+  <si>
+    <t>CompSpec</t>
+  </si>
+  <si>
+    <t>https://iupac.org/fhir/npu/concept-properties#CompSpec</t>
+  </si>
+  <si>
+    <t>Kind-of-property</t>
+  </si>
+  <si>
+    <t>https://iupac.org/fhir/npu/concept-properties#Kind-of-property</t>
+  </si>
+  <si>
+    <t>Speciality</t>
+  </si>
+  <si>
+    <t>https://iupac.org/fhir/npu/concept-properties#Speciality</t>
+  </si>
+  <si>
+    <t>Code value</t>
+  </si>
+  <si>
+    <t>https://iupac.org/fhir/npu/concept-properties#Code-value</t>
+  </si>
+  <si>
+    <t>Scale type</t>
+  </si>
+  <si>
+    <t>https://iupac.org/fhir/npu/concept-properties#Scale-type</t>
+  </si>
+  <si>
+    <t>Proc</t>
+  </si>
+  <si>
+    <t>https://iupac.org/fhir/npu/concept-properties#Proc</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>https://iupac.org/fhir/npu/concept-properties#Unit</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>https://iupac.org/fhir/npu/concept-properties#STATUS</t>
   </si>
   <si>
     <t>Level</t>
@@ -572,7 +650,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -643,6 +721,162 @@
       </c>
       <c r="D5" t="s" s="2">
         <v>54</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -657,159 +891,159 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>36</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>57</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="D3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="D4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="D6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="D7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="D8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="D9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="D10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="D12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="D13" s="2"/>
     </row>

--- a/CodeSystem-dk-npu-fragment.xlsx
+++ b/CodeSystem-dk-npu-fragment.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-27T12:31:37+00:00</t>
+    <t>2024-11-04T14:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-npu-fragment.xlsx
+++ b/CodeSystem-dk-npu-fragment.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:15:57+00:00</t>
+    <t>2024-11-04T14:58:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-npu-fragment.xlsx
+++ b/CodeSystem-dk-npu-fragment.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:58:42+00:00</t>
+    <t>2024-11-04T15:07:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-dk-npu-fragment.xlsx
+++ b/CodeSystem-dk-npu-fragment.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T15:07:28+00:00</t>
+    <t>2024-11-05T12:45:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
